--- a/Behind/july 2026/Pimary VS Secondary.xlsx
+++ b/Behind/july 2026/Pimary VS Secondary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB19693-90CD-4B14-BB4B-EF3C4A4E5C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093D1578-79D2-4B35-BB63-07A02C6B8DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
@@ -709,10 +709,12 @@
         <f t="shared" ref="L7:L13" si="1">J7-K7</f>
         <v>255.02499999999998</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="16">
+        <v>15960</v>
+      </c>
       <c r="N7" s="19">
         <f>L7-M7</f>
-        <v>255.02499999999998</v>
+        <v>-15704.975</v>
       </c>
       <c r="O7" s="17">
         <v>280</v>
@@ -747,10 +749,12 @@
         <f t="shared" si="1"/>
         <v>182.34999999999997</v>
       </c>
-      <c r="M8" s="16"/>
+      <c r="M8" s="16">
+        <v>16223</v>
+      </c>
       <c r="N8" s="19">
         <f t="shared" ref="N8:N13" si="3">L8-M8</f>
-        <v>182.34999999999997</v>
+        <v>-16040.65</v>
       </c>
       <c r="O8" s="17">
         <v>226</v>
@@ -781,10 +785,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M9" s="16"/>
+      <c r="M9" s="16">
+        <v>2800</v>
+      </c>
       <c r="N9" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="O9" s="17">
         <v>41</v>
@@ -819,10 +825,12 @@
         <f t="shared" si="1"/>
         <v>474.375</v>
       </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="16">
+        <v>31878</v>
+      </c>
       <c r="N10" s="19">
         <f t="shared" si="3"/>
-        <v>474.375</v>
+        <v>-31403.625</v>
       </c>
       <c r="O10" s="17">
         <v>64</v>
@@ -857,10 +865,12 @@
         <f t="shared" si="1"/>
         <v>-62.525000000000034</v>
       </c>
-      <c r="M11" s="16"/>
+      <c r="M11" s="16">
+        <v>26490</v>
+      </c>
       <c r="N11" s="19">
         <f t="shared" si="3"/>
-        <v>-62.525000000000034</v>
+        <v>-26552.525000000001</v>
       </c>
       <c r="O11" s="17">
         <v>139</v>
@@ -897,10 +907,12 @@
         <f t="shared" si="1"/>
         <v>977.31499999999994</v>
       </c>
-      <c r="M12" s="16"/>
+      <c r="M12" s="16">
+        <v>38089</v>
+      </c>
       <c r="N12" s="19">
         <f t="shared" si="3"/>
-        <v>977.31499999999994</v>
+        <v>-37111.684999999998</v>
       </c>
       <c r="O12" s="17">
         <v>18</v>
@@ -933,10 +945,12 @@
         <f t="shared" si="1"/>
         <v>1208.72</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="16">
+        <v>35717</v>
+      </c>
       <c r="N13" s="19">
         <f t="shared" si="3"/>
-        <v>1208.72</v>
+        <v>-34508.28</v>
       </c>
       <c r="O13" s="17">
         <v>23</v>
@@ -977,11 +991,11 @@
       </c>
       <c r="M14" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>167157</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="4"/>
-        <v>3035.26</v>
+        <v>-164121.74</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="4"/>
